--- a/docentes/Avila Coronado Julieta - Estadisticos 20241.xlsx
+++ b/docentes/Avila Coronado Julieta - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="24">
   <si>
     <t>Mat</t>
   </si>
@@ -80,6 +80,15 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>MONTIEL</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>MELANIE YARETZI</t>
   </si>
 </sst>
 </file>
@@ -675,16 +684,19 @@
         <v>24</v>
       </c>
       <c r="D2">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>87.5</v>
+      </c>
+      <c r="H2">
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -698,16 +710,19 @@
         <v>36</v>
       </c>
       <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
         <v>36</v>
       </c>
-      <c r="E3">
-        <v>36</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
       <c r="G3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H3">
+        <v>7.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -721,16 +736,19 @@
         <v>28</v>
       </c>
       <c r="D4">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>96.43000000000001</v>
+      </c>
+      <c r="H4">
+        <v>9.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -744,16 +762,19 @@
         <v>35</v>
       </c>
       <c r="D5">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>94.29000000000001</v>
+      </c>
+      <c r="H5">
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -767,16 +788,19 @@
         <v>24</v>
       </c>
       <c r="D6">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>95.83</v>
+      </c>
+      <c r="H6">
+        <v>7.5</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -790,16 +814,19 @@
         <v>37</v>
       </c>
       <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
         <v>37</v>
       </c>
-      <c r="E7">
-        <v>37</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
       <c r="G7">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H7">
+        <v>8.300000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -855,16 +882,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G2">
-        <v>91.67</v>
+        <v>87.5</v>
       </c>
       <c r="H2">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -890,7 +917,7 @@
         <v>100</v>
       </c>
       <c r="H3">
-        <v>7.9</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -916,7 +943,7 @@
         <v>96.43000000000001</v>
       </c>
       <c r="H4">
-        <v>9.1</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -933,16 +960,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G5">
-        <v>91.43000000000001</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="H5">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -959,16 +986,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G6">
-        <v>91.67</v>
+        <v>95.83</v>
       </c>
       <c r="H6">
-        <v>7.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -985,16 +1012,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G7">
-        <v>94.59</v>
+        <v>100</v>
       </c>
       <c r="H7">
-        <v>8.300000000000001</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -1004,7 +1031,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1034,6 +1061,29 @@
         <v>20</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>23330051920259</v>
+      </c>
+      <c r="B2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Avila Coronado Julieta - Estadisticos 20241.xlsx
+++ b/docentes/Avila Coronado Julieta - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="33">
   <si>
     <t>Mat</t>
   </si>
@@ -82,10 +82,37 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>OLMOS</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
     <t>MONTIEL</t>
   </si>
   <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>ORTEGA</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
     <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>JUAN YAHEL</t>
+  </si>
+  <si>
+    <t>ANGEL GABRIEL</t>
+  </si>
+  <si>
+    <t>URIEL</t>
   </si>
   <si>
     <t>MELANIE YARETZI</t>
@@ -1031,7 +1058,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1063,25 +1090,94 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920259</v>
+        <v>23330051920015</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G2">
         <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>23330051920263</v>
+      </c>
+      <c r="B3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>23330051920045</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>23330051920259</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Avila Coronado Julieta - Estadisticos 20241.xlsx
+++ b/docentes/Avila Coronado Julieta - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="39">
   <si>
     <t>Mat</t>
   </si>
@@ -82,6 +82,12 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>TELLO</t>
+  </si>
+  <si>
+    <t>MONTERD</t>
+  </si>
+  <si>
     <t>LUNA</t>
   </si>
   <si>
@@ -94,6 +100,12 @@
     <t>MONTIEL</t>
   </si>
   <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
@@ -104,6 +116,12 @@
   </si>
   <si>
     <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>EMMANUEL</t>
+  </si>
+  <si>
+    <t>ANGEL YAMIL</t>
   </si>
   <si>
     <t>JUAN YAHEL</t>
@@ -1058,7 +1076,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1090,16 +1108,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920015</v>
+        <v>23330051920022</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1108,50 +1126,50 @@
         <v>9</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920263</v>
+        <v>23330051920017</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D3" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920045</v>
+        <v>23330051920015</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1159,16 +1177,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920259</v>
+        <v>23330051920263</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1177,6 +1195,52 @@
         <v>12</v>
       </c>
       <c r="G5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>23330051920045</v>
+      </c>
+      <c r="B6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>23330051920259</v>
+      </c>
+      <c r="B7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Avila Coronado Julieta - Estadisticos 20241.xlsx
+++ b/docentes/Avila Coronado Julieta - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="30">
   <si>
     <t>Mat</t>
   </si>
@@ -82,25 +82,13 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>TELLO</t>
-  </si>
-  <si>
     <t>MONTERD</t>
   </si>
   <si>
     <t>LUNA</t>
   </si>
   <si>
-    <t>OLMOS</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
+    <t>COLMENARES</t>
   </si>
   <si>
     <t>VENTURA</t>
@@ -109,16 +97,7 @@
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>EMMANUEL</t>
+    <t>MARTINEZ</t>
   </si>
   <si>
     <t>ANGEL YAMIL</t>
@@ -127,13 +106,7 @@
     <t>JUAN YAHEL</t>
   </si>
   <si>
-    <t>ANGEL GABRIEL</t>
-  </si>
-  <si>
-    <t>URIEL</t>
-  </si>
-  <si>
-    <t>MELANIE YARETZI</t>
+    <t>JULIO EDUARDO</t>
   </si>
 </sst>
 </file>
@@ -927,13 +900,13 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G2">
-        <v>87.5</v>
+        <v>91.67</v>
       </c>
       <c r="H2">
         <v>8.1</v>
@@ -962,7 +935,7 @@
         <v>100</v>
       </c>
       <c r="H3">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -988,7 +961,7 @@
         <v>96.43000000000001</v>
       </c>
       <c r="H4">
-        <v>9.300000000000001</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1005,16 +978,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G5">
-        <v>94.29000000000001</v>
+        <v>100</v>
       </c>
       <c r="H5">
-        <v>8.1</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1031,16 +1004,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G6">
-        <v>95.83</v>
+        <v>100</v>
       </c>
       <c r="H6">
-        <v>8</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1057,16 +1030,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G7">
-        <v>100</v>
+        <v>97.3</v>
       </c>
       <c r="H7">
-        <v>9.300000000000001</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1076,7 +1049,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1108,16 +1081,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920022</v>
+        <v>23330051920017</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" t="s">
         <v>27</v>
-      </c>
-      <c r="D2" t="s">
-        <v>33</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1126,21 +1099,21 @@
         <v>9</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920017</v>
+        <v>23330051920015</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" t="s">
         <v>28</v>
-      </c>
-      <c r="D3" t="s">
-        <v>34</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1149,99 +1122,30 @@
         <v>9</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920015</v>
+        <v>22330051920424</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" t="s">
         <v>29</v>
       </c>
-      <c r="D4" t="s">
-        <v>35</v>
-      </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G4">
         <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>23330051920263</v>
-      </c>
-      <c r="B5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>23330051920045</v>
-      </c>
-      <c r="B6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D6" t="s">
-        <v>37</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>23330051920259</v>
-      </c>
-      <c r="B7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D7" t="s">
-        <v>38</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Avila Coronado Julieta - Estadisticos 20241.xlsx
+++ b/docentes/Avila Coronado Julieta - Estadisticos 20241.xlsx
@@ -82,28 +82,28 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>LUNA</t>
+  </si>
+  <si>
     <t>MONTERD</t>
   </si>
   <si>
-    <t>LUNA</t>
-  </si>
-  <si>
     <t>COLMENARES</t>
   </si>
   <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
     <t>VENTURA</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
+    <t>JUAN YAHEL</t>
+  </si>
+  <si>
     <t>ANGEL YAMIL</t>
-  </si>
-  <si>
-    <t>JUAN YAHEL</t>
   </si>
   <si>
     <t>JULIO EDUARDO</t>
@@ -1081,7 +1081,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920017</v>
+        <v>23330051920015</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
@@ -1104,7 +1104,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920015</v>
+        <v>23330051920017</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
@@ -1122,7 +1122,7 @@
         <v>9</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:7">
